--- a/ig/ch-core/StructureDefinition-ch-core-ahvn13-identifier.xlsx
+++ b/ig/ch-core/StructureDefinition-ch-core-ahvn13-identifier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>6.0.0</t>
+    <t>7.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T08:02:49+00:00</t>
+    <t>2026-06-10T15:05:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -455,7 +455,7 @@
     <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
-    <t>123456</t>
+    <t>7561234567897</t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
